--- a/web/public/templates/Club-Setup-Template.xlsx
+++ b/web/public/templates/Club-Setup-Template.xlsx
@@ -22,13 +22,13 @@
   <definedNames>
     <definedName name="YesNo">Choices!$A$2:$A$3</definedName>
     <definedName name="Days">Choices!$B$2:$B$8</definedName>
-    <definedName name="EventTypes">Choices!$C$2:$C$4</definedName>
+    <definedName name="EventTypes">Choices!$C$2:$C$5</definedName>
     <definedName name="Repeats">Choices!$D$2:$D$5</definedName>
     <definedName name="Shirts">Choices!$E$2:$E$11</definedName>
     <definedName name="RefGroups">Choices!$F$2:$F$3</definedName>
-    <definedName name="Lists">Choices!$G$2:$G$3</definedName>
+    <definedName name="Lists">Choices!$G$2:$G$4</definedName>
     <definedName name="Programs">Choices!$H$2:$H$4</definedName>
-    <definedName name="DefaultKinds">Choices!$I$2:$I$4</definedName>
+    <definedName name="DefaultKinds">Choices!$I$2:$I$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Club'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Club links'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Club admins'!$1:$1</definedName>
@@ -427,6 +427,21 @@
         <t>Blank = end of the season (June 30).</t>
       </text>
     </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Blank = weekly. Or Every 2 weeks, Every 3 weeks, or None for this one date only.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Like 3, or Courts 3-4.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Practice uniform color. New colors are added to the team's list.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -454,12 +469,22 @@
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>For team events only; tournaments don't repeat.</t>
+        <t>For practices and team events; tournaments don't repeat.</t>
       </text>
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <t>Days of the week, like 'Tue, Thu'.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Practices only.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Practices only.</t>
       </text>
     </comment>
   </commentList>
@@ -1023,7 +1048,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>One row per weekly practice, for a team or a whole group.</t>
+          <t>One row per practice series, for a team or a whole group.</t>
         </is>
       </c>
       <c r="C22" s="6">
@@ -1055,7 +1080,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Optional: the starting handbook and lists for every team.</t>
+          <t>Optional: the starting handbook, lists and practice uniform colors for every team.</t>
         </is>
       </c>
       <c r="C24" s="6">
@@ -1541,7 +1566,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Tournament</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1588,7 +1613,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Tournament</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -1630,7 +1655,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -1641,6 +1666,11 @@
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Youth L</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Practice uniform colors</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -1660,6 +1690,11 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Every 3 weeks</t>
@@ -1668,6 +1703,11 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Youth XL</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Practice uniform colors</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10183,8 +10223,11 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -10225,10 +10268,25 @@
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
+          <t>Repeats</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>Court</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>Uniform color</t>
+        </is>
+      </c>
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -10268,10 +10326,25 @@
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
           <t>A5 Sportsplex</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>Bring both jerseys</t>
         </is>
@@ -10287,6 +10360,9 @@
       <c r="G3" s="15" t="n"/>
       <c r="H3" s="6" t="n"/>
       <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -10298,6 +10374,9 @@
       <c r="G4" s="15" t="n"/>
       <c r="H4" s="6" t="n"/>
       <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -10309,6 +10388,9 @@
       <c r="G5" s="15" t="n"/>
       <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -10320,6 +10402,9 @@
       <c r="G6" s="15" t="n"/>
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -10331,6 +10416,9 @@
       <c r="G7" s="15" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -10342,6 +10430,9 @@
       <c r="G8" s="15" t="n"/>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -10353,6 +10444,9 @@
       <c r="G9" s="15" t="n"/>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -10364,6 +10458,9 @@
       <c r="G10" s="15" t="n"/>
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -10375,6 +10472,9 @@
       <c r="G11" s="15" t="n"/>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -10386,6 +10486,9 @@
       <c r="G12" s="15" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -10397,6 +10500,9 @@
       <c r="G13" s="15" t="n"/>
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -10408,6 +10514,9 @@
       <c r="G14" s="15" t="n"/>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -10419,6 +10528,9 @@
       <c r="G15" s="15" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -10430,6 +10542,9 @@
       <c r="G16" s="15" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -10441,6 +10556,9 @@
       <c r="G17" s="15" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -10452,6 +10570,9 @@
       <c r="G18" s="15" t="n"/>
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -10463,6 +10584,9 @@
       <c r="G19" s="15" t="n"/>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -10474,6 +10598,9 @@
       <c r="G20" s="15" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -10485,6 +10612,9 @@
       <c r="G21" s="15" t="n"/>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -10496,6 +10626,9 @@
       <c r="G22" s="15" t="n"/>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -10507,6 +10640,9 @@
       <c r="G23" s="15" t="n"/>
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -10518,6 +10654,9 @@
       <c r="G24" s="15" t="n"/>
       <c r="H24" s="6" t="n"/>
       <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -10529,6 +10668,9 @@
       <c r="G25" s="15" t="n"/>
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -10540,6 +10682,9 @@
       <c r="G26" s="15" t="n"/>
       <c r="H26" s="6" t="n"/>
       <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -10551,6 +10696,9 @@
       <c r="G27" s="15" t="n"/>
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -10562,6 +10710,9 @@
       <c r="G28" s="15" t="n"/>
       <c r="H28" s="6" t="n"/>
       <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -10573,6 +10724,9 @@
       <c r="G29" s="15" t="n"/>
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -10584,6 +10738,9 @@
       <c r="G30" s="15" t="n"/>
       <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -10595,6 +10752,9 @@
       <c r="G31" s="15" t="n"/>
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -10606,6 +10766,9 @@
       <c r="G32" s="15" t="n"/>
       <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -10617,6 +10780,9 @@
       <c r="G33" s="15" t="n"/>
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -10628,6 +10794,9 @@
       <c r="G34" s="15" t="n"/>
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -10639,6 +10808,9 @@
       <c r="G35" s="15" t="n"/>
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -10650,6 +10822,9 @@
       <c r="G36" s="15" t="n"/>
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -10661,6 +10836,9 @@
       <c r="G37" s="15" t="n"/>
       <c r="H37" s="6" t="n"/>
       <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -10672,6 +10850,9 @@
       <c r="G38" s="15" t="n"/>
       <c r="H38" s="6" t="n"/>
       <c r="I38" s="6" t="n"/>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -10683,6 +10864,9 @@
       <c r="G39" s="15" t="n"/>
       <c r="H39" s="6" t="n"/>
       <c r="I39" s="6" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -10694,6 +10878,9 @@
       <c r="G40" s="15" t="n"/>
       <c r="H40" s="6" t="n"/>
       <c r="I40" s="6" t="n"/>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -10705,6 +10892,9 @@
       <c r="G41" s="15" t="n"/>
       <c r="H41" s="6" t="n"/>
       <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -10716,6 +10906,9 @@
       <c r="G42" s="15" t="n"/>
       <c r="H42" s="6" t="n"/>
       <c r="I42" s="6" t="n"/>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -10727,6 +10920,9 @@
       <c r="G43" s="15" t="n"/>
       <c r="H43" s="6" t="n"/>
       <c r="I43" s="6" t="n"/>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -10738,6 +10934,9 @@
       <c r="G44" s="15" t="n"/>
       <c r="H44" s="6" t="n"/>
       <c r="I44" s="6" t="n"/>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
+      <c r="L44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -10749,6 +10948,9 @@
       <c r="G45" s="15" t="n"/>
       <c r="H45" s="6" t="n"/>
       <c r="I45" s="6" t="n"/>
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="6" t="n"/>
+      <c r="L45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -10760,6 +10962,9 @@
       <c r="G46" s="15" t="n"/>
       <c r="H46" s="6" t="n"/>
       <c r="I46" s="6" t="n"/>
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="n"/>
+      <c r="L46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -10771,6 +10976,9 @@
       <c r="G47" s="15" t="n"/>
       <c r="H47" s="6" t="n"/>
       <c r="I47" s="6" t="n"/>
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="6" t="n"/>
+      <c r="L47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -10782,6 +10990,9 @@
       <c r="G48" s="15" t="n"/>
       <c r="H48" s="6" t="n"/>
       <c r="I48" s="6" t="n"/>
+      <c r="J48" s="6" t="n"/>
+      <c r="K48" s="6" t="n"/>
+      <c r="L48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -10793,6 +11004,9 @@
       <c r="G49" s="15" t="n"/>
       <c r="H49" s="6" t="n"/>
       <c r="I49" s="6" t="n"/>
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="6" t="n"/>
+      <c r="L49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -10804,6 +11018,9 @@
       <c r="G50" s="15" t="n"/>
       <c r="H50" s="6" t="n"/>
       <c r="I50" s="6" t="n"/>
+      <c r="J50" s="6" t="n"/>
+      <c r="K50" s="6" t="n"/>
+      <c r="L50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -10815,6 +11032,9 @@
       <c r="G51" s="15" t="n"/>
       <c r="H51" s="6" t="n"/>
       <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -10826,6 +11046,9 @@
       <c r="G52" s="15" t="n"/>
       <c r="H52" s="6" t="n"/>
       <c r="I52" s="6" t="n"/>
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="6" t="n"/>
+      <c r="L52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -10837,6 +11060,9 @@
       <c r="G53" s="15" t="n"/>
       <c r="H53" s="6" t="n"/>
       <c r="I53" s="6" t="n"/>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="6" t="n"/>
+      <c r="L53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -10848,6 +11074,9 @@
       <c r="G54" s="15" t="n"/>
       <c r="H54" s="6" t="n"/>
       <c r="I54" s="6" t="n"/>
+      <c r="J54" s="6" t="n"/>
+      <c r="K54" s="6" t="n"/>
+      <c r="L54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -10859,6 +11088,9 @@
       <c r="G55" s="15" t="n"/>
       <c r="H55" s="6" t="n"/>
       <c r="I55" s="6" t="n"/>
+      <c r="J55" s="6" t="n"/>
+      <c r="K55" s="6" t="n"/>
+      <c r="L55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -10870,6 +11102,9 @@
       <c r="G56" s="15" t="n"/>
       <c r="H56" s="6" t="n"/>
       <c r="I56" s="6" t="n"/>
+      <c r="J56" s="6" t="n"/>
+      <c r="K56" s="6" t="n"/>
+      <c r="L56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -10881,6 +11116,9 @@
       <c r="G57" s="15" t="n"/>
       <c r="H57" s="6" t="n"/>
       <c r="I57" s="6" t="n"/>
+      <c r="J57" s="6" t="n"/>
+      <c r="K57" s="6" t="n"/>
+      <c r="L57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -10892,6 +11130,9 @@
       <c r="G58" s="15" t="n"/>
       <c r="H58" s="6" t="n"/>
       <c r="I58" s="6" t="n"/>
+      <c r="J58" s="6" t="n"/>
+      <c r="K58" s="6" t="n"/>
+      <c r="L58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -10903,6 +11144,9 @@
       <c r="G59" s="15" t="n"/>
       <c r="H59" s="6" t="n"/>
       <c r="I59" s="6" t="n"/>
+      <c r="J59" s="6" t="n"/>
+      <c r="K59" s="6" t="n"/>
+      <c r="L59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="F60" s="17" t="n"/>
@@ -14669,7 +14913,7 @@
       <c r="G1000" s="17" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the dropdown." type="list">
       <formula1>=Days</formula1>
     </dataValidation>
@@ -14680,6 +14924,9 @@
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Enter a date" error="Enter a date, for example 2026-12-12." type="date" operator="between">
       <formula1>DATE(2020,1,1)</formula1>
       <formula2>DATE(2040,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the dropdown." type="list">
+      <formula1>=Repeats</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14694,7 +14941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T1000"/>
+  <dimension ref="A1:V1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14717,6 +14964,8 @@
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -14818,6 +15067,16 @@
       <c r="T1" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="U1" s="10" t="inlineStr">
+        <is>
+          <t>Court</t>
+        </is>
+      </c>
+      <c r="V1" s="10" t="inlineStr">
+        <is>
+          <t>Uniform color</t>
         </is>
       </c>
     </row>
@@ -14890,6 +15149,8 @@
           <t>Schedules post the Wednesday before.</t>
         </is>
       </c>
+      <c r="U2" s="11" t="inlineStr"/>
+      <c r="V2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -14912,6 +15173,8 @@
       <c r="R3" s="6" t="n"/>
       <c r="S3" s="15" t="n"/>
       <c r="T3" s="6" t="n"/>
+      <c r="U3" s="6" t="n"/>
+      <c r="V3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -14934,6 +15197,8 @@
       <c r="R4" s="6" t="n"/>
       <c r="S4" s="15" t="n"/>
       <c r="T4" s="6" t="n"/>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -14956,6 +15221,8 @@
       <c r="R5" s="6" t="n"/>
       <c r="S5" s="15" t="n"/>
       <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -14978,6 +15245,8 @@
       <c r="R6" s="6" t="n"/>
       <c r="S6" s="15" t="n"/>
       <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -15000,6 +15269,8 @@
       <c r="R7" s="6" t="n"/>
       <c r="S7" s="15" t="n"/>
       <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -15022,6 +15293,8 @@
       <c r="R8" s="6" t="n"/>
       <c r="S8" s="15" t="n"/>
       <c r="T8" s="6" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -15044,6 +15317,8 @@
       <c r="R9" s="6" t="n"/>
       <c r="S9" s="15" t="n"/>
       <c r="T9" s="6" t="n"/>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -15066,6 +15341,8 @@
       <c r="R10" s="6" t="n"/>
       <c r="S10" s="15" t="n"/>
       <c r="T10" s="6" t="n"/>
+      <c r="U10" s="6" t="n"/>
+      <c r="V10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -15088,6 +15365,8 @@
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="15" t="n"/>
       <c r="T11" s="6" t="n"/>
+      <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -15110,6 +15389,8 @@
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="15" t="n"/>
       <c r="T12" s="6" t="n"/>
+      <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -15132,6 +15413,8 @@
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="15" t="n"/>
       <c r="T13" s="6" t="n"/>
+      <c r="U13" s="6" t="n"/>
+      <c r="V13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -15154,6 +15437,8 @@
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="15" t="n"/>
       <c r="T14" s="6" t="n"/>
+      <c r="U14" s="6" t="n"/>
+      <c r="V14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -15176,6 +15461,8 @@
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="15" t="n"/>
       <c r="T15" s="6" t="n"/>
+      <c r="U15" s="6" t="n"/>
+      <c r="V15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -15198,6 +15485,8 @@
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="15" t="n"/>
       <c r="T16" s="6" t="n"/>
+      <c r="U16" s="6" t="n"/>
+      <c r="V16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -15220,6 +15509,8 @@
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="15" t="n"/>
       <c r="T17" s="6" t="n"/>
+      <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -15242,6 +15533,8 @@
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="15" t="n"/>
       <c r="T18" s="6" t="n"/>
+      <c r="U18" s="6" t="n"/>
+      <c r="V18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -15264,6 +15557,8 @@
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="15" t="n"/>
       <c r="T19" s="6" t="n"/>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -15286,6 +15581,8 @@
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="15" t="n"/>
       <c r="T20" s="6" t="n"/>
+      <c r="U20" s="6" t="n"/>
+      <c r="V20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -15308,6 +15605,8 @@
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="15" t="n"/>
       <c r="T21" s="6" t="n"/>
+      <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -15330,6 +15629,8 @@
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="15" t="n"/>
       <c r="T22" s="6" t="n"/>
+      <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -15352,6 +15653,8 @@
       <c r="R23" s="6" t="n"/>
       <c r="S23" s="15" t="n"/>
       <c r="T23" s="6" t="n"/>
+      <c r="U23" s="6" t="n"/>
+      <c r="V23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -15374,6 +15677,8 @@
       <c r="R24" s="6" t="n"/>
       <c r="S24" s="15" t="n"/>
       <c r="T24" s="6" t="n"/>
+      <c r="U24" s="6" t="n"/>
+      <c r="V24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -15396,6 +15701,8 @@
       <c r="R25" s="6" t="n"/>
       <c r="S25" s="15" t="n"/>
       <c r="T25" s="6" t="n"/>
+      <c r="U25" s="6" t="n"/>
+      <c r="V25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -15418,6 +15725,8 @@
       <c r="R26" s="6" t="n"/>
       <c r="S26" s="15" t="n"/>
       <c r="T26" s="6" t="n"/>
+      <c r="U26" s="6" t="n"/>
+      <c r="V26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -15440,6 +15749,8 @@
       <c r="R27" s="6" t="n"/>
       <c r="S27" s="15" t="n"/>
       <c r="T27" s="6" t="n"/>
+      <c r="U27" s="6" t="n"/>
+      <c r="V27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -15462,6 +15773,8 @@
       <c r="R28" s="6" t="n"/>
       <c r="S28" s="15" t="n"/>
       <c r="T28" s="6" t="n"/>
+      <c r="U28" s="6" t="n"/>
+      <c r="V28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -15484,6 +15797,8 @@
       <c r="R29" s="6" t="n"/>
       <c r="S29" s="15" t="n"/>
       <c r="T29" s="6" t="n"/>
+      <c r="U29" s="6" t="n"/>
+      <c r="V29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -15506,6 +15821,8 @@
       <c r="R30" s="6" t="n"/>
       <c r="S30" s="15" t="n"/>
       <c r="T30" s="6" t="n"/>
+      <c r="U30" s="6" t="n"/>
+      <c r="V30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -15528,6 +15845,8 @@
       <c r="R31" s="6" t="n"/>
       <c r="S31" s="15" t="n"/>
       <c r="T31" s="6" t="n"/>
+      <c r="U31" s="6" t="n"/>
+      <c r="V31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -15550,6 +15869,8 @@
       <c r="R32" s="6" t="n"/>
       <c r="S32" s="15" t="n"/>
       <c r="T32" s="6" t="n"/>
+      <c r="U32" s="6" t="n"/>
+      <c r="V32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -15572,6 +15893,8 @@
       <c r="R33" s="6" t="n"/>
       <c r="S33" s="15" t="n"/>
       <c r="T33" s="6" t="n"/>
+      <c r="U33" s="6" t="n"/>
+      <c r="V33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -15594,6 +15917,8 @@
       <c r="R34" s="6" t="n"/>
       <c r="S34" s="15" t="n"/>
       <c r="T34" s="6" t="n"/>
+      <c r="U34" s="6" t="n"/>
+      <c r="V34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -15616,6 +15941,8 @@
       <c r="R35" s="6" t="n"/>
       <c r="S35" s="15" t="n"/>
       <c r="T35" s="6" t="n"/>
+      <c r="U35" s="6" t="n"/>
+      <c r="V35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -15638,6 +15965,8 @@
       <c r="R36" s="6" t="n"/>
       <c r="S36" s="15" t="n"/>
       <c r="T36" s="6" t="n"/>
+      <c r="U36" s="6" t="n"/>
+      <c r="V36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -15660,6 +15989,8 @@
       <c r="R37" s="6" t="n"/>
       <c r="S37" s="15" t="n"/>
       <c r="T37" s="6" t="n"/>
+      <c r="U37" s="6" t="n"/>
+      <c r="V37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -15682,6 +16013,8 @@
       <c r="R38" s="6" t="n"/>
       <c r="S38" s="15" t="n"/>
       <c r="T38" s="6" t="n"/>
+      <c r="U38" s="6" t="n"/>
+      <c r="V38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -15704,6 +16037,8 @@
       <c r="R39" s="6" t="n"/>
       <c r="S39" s="15" t="n"/>
       <c r="T39" s="6" t="n"/>
+      <c r="U39" s="6" t="n"/>
+      <c r="V39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -15726,6 +16061,8 @@
       <c r="R40" s="6" t="n"/>
       <c r="S40" s="15" t="n"/>
       <c r="T40" s="6" t="n"/>
+      <c r="U40" s="6" t="n"/>
+      <c r="V40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -15748,6 +16085,8 @@
       <c r="R41" s="6" t="n"/>
       <c r="S41" s="15" t="n"/>
       <c r="T41" s="6" t="n"/>
+      <c r="U41" s="6" t="n"/>
+      <c r="V41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -15770,6 +16109,8 @@
       <c r="R42" s="6" t="n"/>
       <c r="S42" s="15" t="n"/>
       <c r="T42" s="6" t="n"/>
+      <c r="U42" s="6" t="n"/>
+      <c r="V42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -15792,6 +16133,8 @@
       <c r="R43" s="6" t="n"/>
       <c r="S43" s="15" t="n"/>
       <c r="T43" s="6" t="n"/>
+      <c r="U43" s="6" t="n"/>
+      <c r="V43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -15814,6 +16157,8 @@
       <c r="R44" s="6" t="n"/>
       <c r="S44" s="15" t="n"/>
       <c r="T44" s="6" t="n"/>
+      <c r="U44" s="6" t="n"/>
+      <c r="V44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -15836,6 +16181,8 @@
       <c r="R45" s="6" t="n"/>
       <c r="S45" s="15" t="n"/>
       <c r="T45" s="6" t="n"/>
+      <c r="U45" s="6" t="n"/>
+      <c r="V45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -15858,6 +16205,8 @@
       <c r="R46" s="6" t="n"/>
       <c r="S46" s="15" t="n"/>
       <c r="T46" s="6" t="n"/>
+      <c r="U46" s="6" t="n"/>
+      <c r="V46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -15880,6 +16229,8 @@
       <c r="R47" s="6" t="n"/>
       <c r="S47" s="15" t="n"/>
       <c r="T47" s="6" t="n"/>
+      <c r="U47" s="6" t="n"/>
+      <c r="V47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -15902,6 +16253,8 @@
       <c r="R48" s="6" t="n"/>
       <c r="S48" s="15" t="n"/>
       <c r="T48" s="6" t="n"/>
+      <c r="U48" s="6" t="n"/>
+      <c r="V48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -15924,6 +16277,8 @@
       <c r="R49" s="6" t="n"/>
       <c r="S49" s="15" t="n"/>
       <c r="T49" s="6" t="n"/>
+      <c r="U49" s="6" t="n"/>
+      <c r="V49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -15946,6 +16301,8 @@
       <c r="R50" s="6" t="n"/>
       <c r="S50" s="15" t="n"/>
       <c r="T50" s="6" t="n"/>
+      <c r="U50" s="6" t="n"/>
+      <c r="V50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -15968,6 +16325,8 @@
       <c r="R51" s="6" t="n"/>
       <c r="S51" s="15" t="n"/>
       <c r="T51" s="6" t="n"/>
+      <c r="U51" s="6" t="n"/>
+      <c r="V51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -15990,6 +16349,8 @@
       <c r="R52" s="6" t="n"/>
       <c r="S52" s="15" t="n"/>
       <c r="T52" s="6" t="n"/>
+      <c r="U52" s="6" t="n"/>
+      <c r="V52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -16012,6 +16373,8 @@
       <c r="R53" s="6" t="n"/>
       <c r="S53" s="15" t="n"/>
       <c r="T53" s="6" t="n"/>
+      <c r="U53" s="6" t="n"/>
+      <c r="V53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -16034,6 +16397,8 @@
       <c r="R54" s="6" t="n"/>
       <c r="S54" s="15" t="n"/>
       <c r="T54" s="6" t="n"/>
+      <c r="U54" s="6" t="n"/>
+      <c r="V54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -16056,6 +16421,8 @@
       <c r="R55" s="6" t="n"/>
       <c r="S55" s="15" t="n"/>
       <c r="T55" s="6" t="n"/>
+      <c r="U55" s="6" t="n"/>
+      <c r="V55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -16078,6 +16445,8 @@
       <c r="R56" s="6" t="n"/>
       <c r="S56" s="15" t="n"/>
       <c r="T56" s="6" t="n"/>
+      <c r="U56" s="6" t="n"/>
+      <c r="V56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -16100,6 +16469,8 @@
       <c r="R57" s="6" t="n"/>
       <c r="S57" s="15" t="n"/>
       <c r="T57" s="6" t="n"/>
+      <c r="U57" s="6" t="n"/>
+      <c r="V57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -16122,6 +16493,8 @@
       <c r="R58" s="6" t="n"/>
       <c r="S58" s="15" t="n"/>
       <c r="T58" s="6" t="n"/>
+      <c r="U58" s="6" t="n"/>
+      <c r="V58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -16144,6 +16517,8 @@
       <c r="R59" s="6" t="n"/>
       <c r="S59" s="15" t="n"/>
       <c r="T59" s="6" t="n"/>
+      <c r="U59" s="6" t="n"/>
+      <c r="V59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="D60" s="17" t="n"/>

--- a/web/public/templates/Club-Setup-Template.xlsx
+++ b/web/public/templates/Club-Setup-Template.xlsx
@@ -442,6 +442,11 @@
         <t>Practice uniform color. New colors are added to the team's list.</t>
       </text>
     </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Street address. Families get a map link; without one the map searches the location.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -485,6 +490,16 @@
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>Practices only.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>Street address of the venue. Families get a map link; without one the map searches the venue and city.</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>Travel tournaments: the team hotel's street address.</t>
       </text>
     </comment>
   </commentList>
@@ -10213,7 +10228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L1000"/>
+  <dimension ref="A1:M1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10228,6 +10243,7 @@
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -10291,6 +10307,11 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="M1" s="10" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -10347,6 +10368,11 @@
       <c r="L2" s="11" t="inlineStr">
         <is>
           <t>Bring both jerseys</t>
+        </is>
+      </c>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>1234 Example Rd, Roswell, GA 30076</t>
         </is>
       </c>
     </row>
@@ -10363,6 +10389,7 @@
       <c r="J3" s="6" t="n"/>
       <c r="K3" s="6" t="n"/>
       <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -10377,6 +10404,7 @@
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -10391,6 +10419,7 @@
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -10405,6 +10434,7 @@
       <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -10419,6 +10449,7 @@
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -10433,6 +10464,7 @@
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -10447,6 +10479,7 @@
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
       <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -10461,6 +10494,7 @@
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -10475,6 +10509,7 @@
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
       <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -10489,6 +10524,7 @@
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
       <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -10503,6 +10539,7 @@
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
       <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -10517,6 +10554,7 @@
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
       <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -10531,6 +10569,7 @@
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
       <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -10545,6 +10584,7 @@
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -10559,6 +10599,7 @@
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -10573,6 +10614,7 @@
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -10587,6 +10629,7 @@
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
       <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -10601,6 +10644,7 @@
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
       <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -10615,6 +10659,7 @@
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -10629,6 +10674,7 @@
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
       <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -10643,6 +10689,7 @@
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -10657,6 +10704,7 @@
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
       <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -10671,6 +10719,7 @@
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
       <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -10685,6 +10734,7 @@
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
       <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -10699,6 +10749,7 @@
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
       <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -10713,6 +10764,7 @@
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -10727,6 +10779,7 @@
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
       <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -10741,6 +10794,7 @@
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
       <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -10755,6 +10809,7 @@
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
       <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -10769,6 +10824,7 @@
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -10783,6 +10839,7 @@
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
       <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -10797,6 +10854,7 @@
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -10811,6 +10869,7 @@
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="n"/>
       <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -10825,6 +10884,7 @@
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -10839,6 +10899,7 @@
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="n"/>
       <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -10853,6 +10914,7 @@
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="n"/>
       <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -10867,6 +10929,7 @@
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="n"/>
       <c r="L39" s="6" t="n"/>
+      <c r="M39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -10881,6 +10944,7 @@
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="n"/>
       <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -10895,6 +10959,7 @@
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="n"/>
       <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -10909,6 +10974,7 @@
       <c r="J42" s="6" t="n"/>
       <c r="K42" s="6" t="n"/>
       <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -10923,6 +10989,7 @@
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
       <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -10937,6 +11004,7 @@
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="6" t="n"/>
       <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -10951,6 +11019,7 @@
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="6" t="n"/>
       <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -10965,6 +11034,7 @@
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="6" t="n"/>
+      <c r="M46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -10979,6 +11049,7 @@
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
       <c r="L47" s="6" t="n"/>
+      <c r="M47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -10993,6 +11064,7 @@
       <c r="J48" s="6" t="n"/>
       <c r="K48" s="6" t="n"/>
       <c r="L48" s="6" t="n"/>
+      <c r="M48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -11007,6 +11079,7 @@
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="6" t="n"/>
       <c r="L49" s="6" t="n"/>
+      <c r="M49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -11021,6 +11094,7 @@
       <c r="J50" s="6" t="n"/>
       <c r="K50" s="6" t="n"/>
       <c r="L50" s="6" t="n"/>
+      <c r="M50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -11035,6 +11109,7 @@
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="6" t="n"/>
       <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -11049,6 +11124,7 @@
       <c r="J52" s="6" t="n"/>
       <c r="K52" s="6" t="n"/>
       <c r="L52" s="6" t="n"/>
+      <c r="M52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -11063,6 +11139,7 @@
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="6" t="n"/>
       <c r="L53" s="6" t="n"/>
+      <c r="M53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -11077,6 +11154,7 @@
       <c r="J54" s="6" t="n"/>
       <c r="K54" s="6" t="n"/>
       <c r="L54" s="6" t="n"/>
+      <c r="M54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -11091,6 +11169,7 @@
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="6" t="n"/>
       <c r="L55" s="6" t="n"/>
+      <c r="M55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -11105,6 +11184,7 @@
       <c r="J56" s="6" t="n"/>
       <c r="K56" s="6" t="n"/>
       <c r="L56" s="6" t="n"/>
+      <c r="M56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -11119,6 +11199,7 @@
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="6" t="n"/>
       <c r="L57" s="6" t="n"/>
+      <c r="M57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -11133,6 +11214,7 @@
       <c r="J58" s="6" t="n"/>
       <c r="K58" s="6" t="n"/>
       <c r="L58" s="6" t="n"/>
+      <c r="M58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -11147,6 +11229,7 @@
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="6" t="n"/>
       <c r="L59" s="6" t="n"/>
+      <c r="M59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="F60" s="17" t="n"/>
@@ -14941,7 +15024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V1000"/>
+  <dimension ref="A1:X1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14966,6 +15049,8 @@
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -15077,6 +15162,16 @@
       <c r="V1" s="10" t="inlineStr">
         <is>
           <t>Uniform color</t>
+        </is>
+      </c>
+      <c r="W1" s="10" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="X1" s="10" t="inlineStr">
+        <is>
+          <t>Hotel address</t>
         </is>
       </c>
     </row>
@@ -15151,6 +15246,12 @@
       </c>
       <c r="U2" s="11" t="inlineStr"/>
       <c r="V2" s="11" t="inlineStr"/>
+      <c r="W2" s="11" t="inlineStr">
+        <is>
+          <t>285 Andrew Young International Blvd NW, Atlanta, GA 30313</t>
+        </is>
+      </c>
+      <c r="X2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -15175,6 +15276,8 @@
       <c r="T3" s="6" t="n"/>
       <c r="U3" s="6" t="n"/>
       <c r="V3" s="6" t="n"/>
+      <c r="W3" s="6" t="n"/>
+      <c r="X3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -15199,6 +15302,8 @@
       <c r="T4" s="6" t="n"/>
       <c r="U4" s="6" t="n"/>
       <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -15223,6 +15328,8 @@
       <c r="T5" s="6" t="n"/>
       <c r="U5" s="6" t="n"/>
       <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -15247,6 +15354,8 @@
       <c r="T6" s="6" t="n"/>
       <c r="U6" s="6" t="n"/>
       <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -15271,6 +15380,8 @@
       <c r="T7" s="6" t="n"/>
       <c r="U7" s="6" t="n"/>
       <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -15295,6 +15406,8 @@
       <c r="T8" s="6" t="n"/>
       <c r="U8" s="6" t="n"/>
       <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -15319,6 +15432,8 @@
       <c r="T9" s="6" t="n"/>
       <c r="U9" s="6" t="n"/>
       <c r="V9" s="6" t="n"/>
+      <c r="W9" s="6" t="n"/>
+      <c r="X9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -15343,6 +15458,8 @@
       <c r="T10" s="6" t="n"/>
       <c r="U10" s="6" t="n"/>
       <c r="V10" s="6" t="n"/>
+      <c r="W10" s="6" t="n"/>
+      <c r="X10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -15367,6 +15484,8 @@
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
+      <c r="X11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -15391,6 +15510,8 @@
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
+      <c r="X12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -15415,6 +15536,8 @@
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
+      <c r="W13" s="6" t="n"/>
+      <c r="X13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -15439,6 +15562,8 @@
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
+      <c r="W14" s="6" t="n"/>
+      <c r="X14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -15463,6 +15588,8 @@
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
+      <c r="X15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -15487,6 +15614,8 @@
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
+      <c r="W16" s="6" t="n"/>
+      <c r="X16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -15511,6 +15640,8 @@
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
+      <c r="X17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -15535,6 +15666,8 @@
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
+      <c r="W18" s="6" t="n"/>
+      <c r="X18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -15559,6 +15692,8 @@
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
+      <c r="X19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -15583,6 +15718,8 @@
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
+      <c r="W20" s="6" t="n"/>
+      <c r="X20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -15607,6 +15744,8 @@
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
+      <c r="X21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -15631,6 +15770,8 @@
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -15655,6 +15796,8 @@
       <c r="T23" s="6" t="n"/>
       <c r="U23" s="6" t="n"/>
       <c r="V23" s="6" t="n"/>
+      <c r="W23" s="6" t="n"/>
+      <c r="X23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -15679,6 +15822,8 @@
       <c r="T24" s="6" t="n"/>
       <c r="U24" s="6" t="n"/>
       <c r="V24" s="6" t="n"/>
+      <c r="W24" s="6" t="n"/>
+      <c r="X24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -15703,6 +15848,8 @@
       <c r="T25" s="6" t="n"/>
       <c r="U25" s="6" t="n"/>
       <c r="V25" s="6" t="n"/>
+      <c r="W25" s="6" t="n"/>
+      <c r="X25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -15727,6 +15874,8 @@
       <c r="T26" s="6" t="n"/>
       <c r="U26" s="6" t="n"/>
       <c r="V26" s="6" t="n"/>
+      <c r="W26" s="6" t="n"/>
+      <c r="X26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -15751,6 +15900,8 @@
       <c r="T27" s="6" t="n"/>
       <c r="U27" s="6" t="n"/>
       <c r="V27" s="6" t="n"/>
+      <c r="W27" s="6" t="n"/>
+      <c r="X27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -15775,6 +15926,8 @@
       <c r="T28" s="6" t="n"/>
       <c r="U28" s="6" t="n"/>
       <c r="V28" s="6" t="n"/>
+      <c r="W28" s="6" t="n"/>
+      <c r="X28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -15799,6 +15952,8 @@
       <c r="T29" s="6" t="n"/>
       <c r="U29" s="6" t="n"/>
       <c r="V29" s="6" t="n"/>
+      <c r="W29" s="6" t="n"/>
+      <c r="X29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -15823,6 +15978,8 @@
       <c r="T30" s="6" t="n"/>
       <c r="U30" s="6" t="n"/>
       <c r="V30" s="6" t="n"/>
+      <c r="W30" s="6" t="n"/>
+      <c r="X30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -15847,6 +16004,8 @@
       <c r="T31" s="6" t="n"/>
       <c r="U31" s="6" t="n"/>
       <c r="V31" s="6" t="n"/>
+      <c r="W31" s="6" t="n"/>
+      <c r="X31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -15871,6 +16030,8 @@
       <c r="T32" s="6" t="n"/>
       <c r="U32" s="6" t="n"/>
       <c r="V32" s="6" t="n"/>
+      <c r="W32" s="6" t="n"/>
+      <c r="X32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -15895,6 +16056,8 @@
       <c r="T33" s="6" t="n"/>
       <c r="U33" s="6" t="n"/>
       <c r="V33" s="6" t="n"/>
+      <c r="W33" s="6" t="n"/>
+      <c r="X33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -15919,6 +16082,8 @@
       <c r="T34" s="6" t="n"/>
       <c r="U34" s="6" t="n"/>
       <c r="V34" s="6" t="n"/>
+      <c r="W34" s="6" t="n"/>
+      <c r="X34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -15943,6 +16108,8 @@
       <c r="T35" s="6" t="n"/>
       <c r="U35" s="6" t="n"/>
       <c r="V35" s="6" t="n"/>
+      <c r="W35" s="6" t="n"/>
+      <c r="X35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -15967,6 +16134,8 @@
       <c r="T36" s="6" t="n"/>
       <c r="U36" s="6" t="n"/>
       <c r="V36" s="6" t="n"/>
+      <c r="W36" s="6" t="n"/>
+      <c r="X36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -15991,6 +16160,8 @@
       <c r="T37" s="6" t="n"/>
       <c r="U37" s="6" t="n"/>
       <c r="V37" s="6" t="n"/>
+      <c r="W37" s="6" t="n"/>
+      <c r="X37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -16015,6 +16186,8 @@
       <c r="T38" s="6" t="n"/>
       <c r="U38" s="6" t="n"/>
       <c r="V38" s="6" t="n"/>
+      <c r="W38" s="6" t="n"/>
+      <c r="X38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -16039,6 +16212,8 @@
       <c r="T39" s="6" t="n"/>
       <c r="U39" s="6" t="n"/>
       <c r="V39" s="6" t="n"/>
+      <c r="W39" s="6" t="n"/>
+      <c r="X39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -16063,6 +16238,8 @@
       <c r="T40" s="6" t="n"/>
       <c r="U40" s="6" t="n"/>
       <c r="V40" s="6" t="n"/>
+      <c r="W40" s="6" t="n"/>
+      <c r="X40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -16087,6 +16264,8 @@
       <c r="T41" s="6" t="n"/>
       <c r="U41" s="6" t="n"/>
       <c r="V41" s="6" t="n"/>
+      <c r="W41" s="6" t="n"/>
+      <c r="X41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -16111,6 +16290,8 @@
       <c r="T42" s="6" t="n"/>
       <c r="U42" s="6" t="n"/>
       <c r="V42" s="6" t="n"/>
+      <c r="W42" s="6" t="n"/>
+      <c r="X42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -16135,6 +16316,8 @@
       <c r="T43" s="6" t="n"/>
       <c r="U43" s="6" t="n"/>
       <c r="V43" s="6" t="n"/>
+      <c r="W43" s="6" t="n"/>
+      <c r="X43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -16159,6 +16342,8 @@
       <c r="T44" s="6" t="n"/>
       <c r="U44" s="6" t="n"/>
       <c r="V44" s="6" t="n"/>
+      <c r="W44" s="6" t="n"/>
+      <c r="X44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -16183,6 +16368,8 @@
       <c r="T45" s="6" t="n"/>
       <c r="U45" s="6" t="n"/>
       <c r="V45" s="6" t="n"/>
+      <c r="W45" s="6" t="n"/>
+      <c r="X45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -16207,6 +16394,8 @@
       <c r="T46" s="6" t="n"/>
       <c r="U46" s="6" t="n"/>
       <c r="V46" s="6" t="n"/>
+      <c r="W46" s="6" t="n"/>
+      <c r="X46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -16231,6 +16420,8 @@
       <c r="T47" s="6" t="n"/>
       <c r="U47" s="6" t="n"/>
       <c r="V47" s="6" t="n"/>
+      <c r="W47" s="6" t="n"/>
+      <c r="X47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -16255,6 +16446,8 @@
       <c r="T48" s="6" t="n"/>
       <c r="U48" s="6" t="n"/>
       <c r="V48" s="6" t="n"/>
+      <c r="W48" s="6" t="n"/>
+      <c r="X48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -16279,6 +16472,8 @@
       <c r="T49" s="6" t="n"/>
       <c r="U49" s="6" t="n"/>
       <c r="V49" s="6" t="n"/>
+      <c r="W49" s="6" t="n"/>
+      <c r="X49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -16303,6 +16498,8 @@
       <c r="T50" s="6" t="n"/>
       <c r="U50" s="6" t="n"/>
       <c r="V50" s="6" t="n"/>
+      <c r="W50" s="6" t="n"/>
+      <c r="X50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -16327,6 +16524,8 @@
       <c r="T51" s="6" t="n"/>
       <c r="U51" s="6" t="n"/>
       <c r="V51" s="6" t="n"/>
+      <c r="W51" s="6" t="n"/>
+      <c r="X51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -16351,6 +16550,8 @@
       <c r="T52" s="6" t="n"/>
       <c r="U52" s="6" t="n"/>
       <c r="V52" s="6" t="n"/>
+      <c r="W52" s="6" t="n"/>
+      <c r="X52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -16375,6 +16576,8 @@
       <c r="T53" s="6" t="n"/>
       <c r="U53" s="6" t="n"/>
       <c r="V53" s="6" t="n"/>
+      <c r="W53" s="6" t="n"/>
+      <c r="X53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -16399,6 +16602,8 @@
       <c r="T54" s="6" t="n"/>
       <c r="U54" s="6" t="n"/>
       <c r="V54" s="6" t="n"/>
+      <c r="W54" s="6" t="n"/>
+      <c r="X54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -16423,6 +16628,8 @@
       <c r="T55" s="6" t="n"/>
       <c r="U55" s="6" t="n"/>
       <c r="V55" s="6" t="n"/>
+      <c r="W55" s="6" t="n"/>
+      <c r="X55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -16447,6 +16654,8 @@
       <c r="T56" s="6" t="n"/>
       <c r="U56" s="6" t="n"/>
       <c r="V56" s="6" t="n"/>
+      <c r="W56" s="6" t="n"/>
+      <c r="X56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -16471,6 +16680,8 @@
       <c r="T57" s="6" t="n"/>
       <c r="U57" s="6" t="n"/>
       <c r="V57" s="6" t="n"/>
+      <c r="W57" s="6" t="n"/>
+      <c r="X57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -16495,6 +16706,8 @@
       <c r="T58" s="6" t="n"/>
       <c r="U58" s="6" t="n"/>
       <c r="V58" s="6" t="n"/>
+      <c r="W58" s="6" t="n"/>
+      <c r="X58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -16519,6 +16732,8 @@
       <c r="T59" s="6" t="n"/>
       <c r="U59" s="6" t="n"/>
       <c r="V59" s="6" t="n"/>
+      <c r="W59" s="6" t="n"/>
+      <c r="X59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="D60" s="17" t="n"/>

--- a/web/public/templates/Club-Setup-Template.xlsx
+++ b/web/public/templates/Club-Setup-Template.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice patterns" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shared schedule" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defaults" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choices" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team lists" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choices" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="YesNo">Choices!$A$2:$A$3</definedName>
@@ -26,7 +27,7 @@
     <definedName name="Repeats">Choices!$D$2:$D$5</definedName>
     <definedName name="Shirts">Choices!$E$2:$E$11</definedName>
     <definedName name="RefGroups">Choices!$F$2:$F$3</definedName>
-    <definedName name="Lists">Choices!$G$2:$G$4</definedName>
+    <definedName name="Lists">Choices!$G$2:$G$5</definedName>
     <definedName name="Programs">Choices!$H$2:$H$4</definedName>
     <definedName name="DefaultKinds">Choices!$I$2:$I$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Club'!$1:$1</definedName>
@@ -38,6 +39,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Practice patterns'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Shared schedule'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Defaults'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Team lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -239,7 +241,7 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -274,7 +276,7 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -289,7 +291,7 @@
 <file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -314,7 +316,7 @@
 <file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -354,7 +356,7 @@
 <file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -409,7 +411,7 @@
 <file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -454,7 +456,7 @@
 <file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -509,10 +511,30 @@
 <file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>For handbook sections.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Teem Hub</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Must match a Team ID on the Teams tab.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>For handbook sections.</t>
       </text>
@@ -810,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -828,7 +850,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fill in this workbook to set up a whole club in Team Hub at once: the club's look and links, every team, its staff and roster, practices by age group and the tournaments teams share. Club admins and site owners upload it from the club page.</t>
+          <t>Fill in this workbook to set up a whole club in Teem Hub at once: the club's look and links, every team, its staff and roster, practices by age group and the tournaments teams share. Club admins and site owners upload it from the club page.</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1125,26 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Team lists</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Optional: one team's own handbook and lists, replacing the defaults for that team.</t>
+        </is>
+      </c>
+      <c r="C25" s="6">
+        <f>COUNTA('Team lists'!A3:A1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>When you upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>You see a preview first: what will be created, and each problem by tab and row. Nothing is saved until you confirm.</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1156,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Uploading again updates what's there instead of adding duplicates. Teams match on Team ID, players on jersey or name, events on type, date and title, people on email. Blank cells keep what's saved.</t>
+          <t>You see a preview first: what will be created, and each problem by tab and row. Nothing is saved until you confirm.</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1168,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Nothing is removed: players, events and people already on a team but not in the workbook stay, and so do answers, payments and travel plans families entered.</t>
+          <t>Uploading again updates what's there instead of adding duplicates. Teams match on Team ID, players on jersey or name, events on type, date and title, people on email. Blank cells keep what's saved.</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1180,19 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Each person marked for an invite gets the right role, linked to their player, as soon as they sign in or create an account with that email. Team Hub doesn't email them yet, so let them know.</t>
+          <t>Nothing is removed: players, events and people already on a team but not in the workbook stay, and so do answers, payments and travel plans families entered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Each person marked for an invite gets the right role, linked to their player, as soon as they sign in or create an account with that email. Teem Hub doesn't email them yet, so let them know.</t>
         </is>
       </c>
     </row>
@@ -1516,6 +1554,418 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Team ID *</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>List *</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Text or item *</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>a5-13-tom</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Packing checklist</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr"/>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Knee and elbow pads</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown team" error="Use a Team ID from the Teams tab." type="list">
+      <formula1>=Teams!$A$2:$A$1000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the dropdown." type="list">
+      <formula1>=Lists</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I11"/>
@@ -1718,6 +2168,11 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Youth XL</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Handbook section</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">

--- a/web/public/templates/Club-Setup-Template.xlsx
+++ b/web/public/templates/Club-Setup-Template.xlsx
@@ -543,6 +543,36 @@
 </comments>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="495300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -832,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A2:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -840,323 +870,312 @@
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="44" customHeight="1"/>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Club setup</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Fill in this workbook to set up a whole club in Teem Hub at once: the club's look and links, every team, its staff and roster, practices by age group and the tournaments teams share. Club admins and site owners upload it from the club page.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>How to fill it in</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Red header *</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Required column. Rows missing it are listed as problems in the upload preview.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Navy header</t>
+          <t>Red header *</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Optional column.</t>
+          <t>Required column. Rows missing it are listed as problems in the upload preview.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Grey italic row 2</t>
+          <t>Navy header</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>An example showing the format. Type over it or delete it; it is skipped if left unchanged.</t>
+          <t>Optional column.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Dropdown cells</t>
+          <t>Grey italic row 2</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Pick from the list. Hover over a header for a note on that column.</t>
+          <t>An example showing the format. Type over it or delete it; it is skipped if left unchanged.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Dropdown cells</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Any Excel date, or text like 2026-12-12.</t>
+          <t>Pick from the list. Hover over a header for a note on that column.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Times</t>
+          <t>Dates</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Text like 6:30 PM.</t>
+          <t>Any Excel date, or text like 2026-12-12.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Leave out</t>
+          <t>Times</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Availability, travel plans, uniform sizes, meal claims and payments: families enter these themselves. Never add passwords.</t>
+          <t>Text like 6:30 PM.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Team ID</t>
+          <t>Leave out</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Lowercase letters, numbers and dashes, like a5-13-tom. It becomes part of the team's web address and can't be changed later.</t>
+          <t>Availability, travel plans, uniform sizes, meal claims and payments: families enter these themselves. Never add passwords.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Team ID</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Lowercase letters, numbers and dashes, like a5-13-tom. It becomes part of the team's web address and can't be changed later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>Groups</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>On Practice patterns and Shared schedule you can name a group instead of listing teams: All, All National, All Regional, All Boys, an age group like 13U, or both like 13U National. Or list Team IDs separated by commas.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Tabs</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Rows filled</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Club</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>One row: the club's name, colors and notes for every team.</t>
         </is>
       </c>
-      <c r="C16" s="6">
+      <c r="C17" s="6">
         <f>COUNTA(Club!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Club links</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Links every team sees on Team Info.</t>
         </is>
       </c>
-      <c r="C17" s="6">
+      <c r="C18" s="6">
         <f>COUNTA('Club links'!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Club admins</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>People who run the club; they get club-admin invites.</t>
         </is>
       </c>
-      <c r="C18" s="6">
+      <c r="C19" s="6">
         <f>COUNTA('Club admins'!C3:C1000)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Teams</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>One row per team. Every other tab refers to teams by Team ID.</t>
         </is>
       </c>
-      <c r="C19" s="6">
+      <c r="C20" s="6">
         <f>COUNTA(Teams!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>One row per person per team. A coach on two teams has two rows.</t>
         </is>
       </c>
-      <c r="C20" s="6">
+      <c r="C21" s="6">
         <f>COUNTA(Staff!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Rosters</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>One row per player, all teams together.</t>
         </is>
       </c>
-      <c r="C21" s="6">
+      <c r="C22" s="6">
         <f>COUNTA(Rosters!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Practice patterns</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>One row per practice series, for a team or a whole group.</t>
         </is>
       </c>
-      <c r="C22" s="6">
+      <c r="C23" s="6">
         <f>COUNTA('Practice patterns'!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Shared schedule</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Tournaments and events, each listed once for all the teams going.</t>
         </is>
       </c>
-      <c r="C23" s="6">
+      <c r="C24" s="6">
         <f>COUNTA('Shared schedule'!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Defaults</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Optional: the starting handbook, lists and practice uniform colors for every team.</t>
         </is>
       </c>
-      <c r="C24" s="6">
+      <c r="C25" s="6">
         <f>COUNTA(Defaults!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Team lists</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Optional: one team's own handbook and lists, replacing the defaults for that team.</t>
         </is>
       </c>
-      <c r="C25" s="6">
+      <c r="C26" s="6">
         <f>COUNTA('Team lists'!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>When you upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>You see a preview first: what will be created, and each problem by tab and row. Nothing is saved until you confirm.</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1187,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Uploading again updates what's there instead of adding duplicates. Teams match on Team ID, players on jersey or name, events on type, date and title, people on email. Blank cells keep what's saved.</t>
+          <t>You see a preview first: what will be created, and each problem by tab and row. Nothing is saved until you confirm.</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1199,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Nothing is removed: players, events and people already on a team but not in the workbook stay, and so do answers, payments and travel plans families entered.</t>
+          <t>Uploading again updates what's there instead of adding duplicates. Teams match on Team ID, players on jersey or name, events on type, date and title, people on email. Blank cells keep what's saved.</t>
         </is>
       </c>
     </row>
@@ -1192,16 +1211,29 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
+          <t>Nothing is removed: players, events and people already on a team but not in the workbook stay, and so do answers, payments and travel plans families entered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
           <t>Each person marked for an invite gets the right role, linked to their player, as soon as they sign in or create an account with that email. Teem Hub doesn't email them yet, so let them know.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
